--- a/workbooks/unit-c-functions.xlsx
+++ b/workbooks/unit-c-functions.xlsx
@@ -24,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,12 +53,18 @@
     <font>
       <name val="Arial"/>
       <i val="1"/>
-      <color rgb="00777777"/>
+      <color rgb="00555555"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
-      <i val="1"/>
+      <b val="1"/>
+      <color rgb="001F4E8C"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10.5"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -66,10 +72,22 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="001F4E8C"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
       <name val="Courier New"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00777777"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -83,11 +101,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00DCEEFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F8FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -95,11 +123,69 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="004F9DFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="004F9DFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="004F9DFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="004F9DFF"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="004F9DFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="004F9DFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="004F9DFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="004F9DFF"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="004F9DFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="004F9DFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="004F9DFF"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="004F9DFF"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="004F9DFF"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="004F9DFF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -108,9 +194,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -185,6 +286,71 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Excel for Finance course</author>
+  </authors>
+  <commentList>
+    <comment ref="B9" authorId="0" shapeId="0">
+      <text>
+        <t>Type =FV(B6,B7,0,-B5) here.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Excel for Finance course</author>
+  </authors>
+  <commentList>
+    <comment ref="B12" authorId="0" shapeId="0">
+      <text>
+        <t>Copy the formula from the cell directly above (row 11) down into this cell.</t>
+      </text>
+    </comment>
+    <comment ref="C12" authorId="0" shapeId="0">
+      <text>
+        <t>Copy the formula from the cell directly above (row 11) down into this cell.</t>
+      </text>
+    </comment>
+    <comment ref="D12" authorId="0" shapeId="0">
+      <text>
+        <t>Copy the formula from the cell directly above (row 11) down into this cell.</t>
+      </text>
+    </comment>
+    <comment ref="E12" authorId="0" shapeId="0">
+      <text>
+        <t>Copy the formula from the cell directly above (row 11) down into this cell.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Excel for Finance course</author>
+  </authors>
+  <commentList>
+    <comment ref="B13" authorId="0" shapeId="0">
+      <text>
+        <t>Type =NPV(B11,B7:B9)+B6 here.</t>
+      </text>
+    </comment>
+    <comment ref="B14" authorId="0" shapeId="0">
+      <text>
+        <t>Type =IRR(B6:B9) here.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -476,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -500,28 +666,56 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>How to use this workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Each tab has a blue 'YOUR TASK' box with numbered steps — read it first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Yellow cells also have a small red comment triangle in the corner — hover over one for a quick reminder of exactly what to type.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Compare your work against the 'Answer Key' tab at the end — it recalculates live, so it updates as you fill things in. (C4 is an exploration exercise with no single right answer, so it isn't in the Answer Key.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
           <t>Color legend:</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Yellow fill</t>
         </is>
       </c>
-      <c r="B5">
+      <c r="B10">
         <f> a cell you should fill in</f>
         <v/>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Blue text</t>
         </is>
       </c>
-      <c r="B6">
+      <c r="B11">
         <f> a hardcoded input/assumption</f>
         <v/>
       </c>
@@ -537,7 +731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -561,7 +755,7 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Yellow cells are for you to fill in. Everything else is provided.</t>
+          <t>🟡 Yellow cell = type something here.   🔵 Blue text = a given input.   Black text = a formula already provided.</t>
         </is>
       </c>
     </row>
@@ -609,19 +803,55 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Task: use FV(rate, years, 0, -amount) to find the future value. Remember: money invested today is cash OUT, so it goes in as a negative.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+          <t>✏️  YOUR TASK</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>1. In B9, use the FV function: =FV(rate, years, 0, -amount).</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>2. The rate is in B6, years in B7, amount invested in B5.</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="n"/>
+    </row>
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>3. Enter the amount (B5) as NEGATIVE inside the formula — money invested today is cash going OUT, so its sign should be negative for FV's sign convention to give you a positive answer back.</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="14" t="n"/>
+      <c r="E14" s="14" t="n"/>
+      <c r="F14" s="15" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="7">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A12:F12"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A11:F12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -631,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -658,7 +888,7 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Yellow cells are for you to fill in. Everything else is provided.</t>
+          <t>🟡 Yellow cell = type something here.   🔵 Blue text = a given input.   Black text = a formula already provided.</t>
         </is>
       </c>
     </row>
@@ -695,27 +925,27 @@
     </row>
     <row r="8"/>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>Payment</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>Interest</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>Principal</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>Balance</t>
         </is>
@@ -800,20 +1030,64 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Task: rows 12-16 (months 2-6) are blank. Copy every formula from row 11 down — Payment/Interest/Principal use the loan inputs (locked with $) and the period number (relative, column A); Balance = the row above's balance minus this period's principal, so it also copies down cleanly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20"/>
+          <t>✏️  YOUR TASK</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>1. Row 11 (Period 1) is fully worked out for you — look at its 4 formulas before continuing.</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="n"/>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>2. Select B11:E11 (all 4 of Period 1's formulas), copy them, then paste into B12:E16 (Periods 2 through 6). Or drag the fill handle from E11 down through E16, then repeat for columns B-D.</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>3. Payment/Interest/Principal use $-locked references to the loan inputs, so they stay correct wherever you paste them. Balance references the row directly above it, so it also chains correctly down the column.</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>💡 Sanity check: the Balance in row 16 should be noticeably smaller than in row 11, and Interest should shrink each period while Principal grows.</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="14" t="n"/>
+      <c r="F22" s="15" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="8">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A18:F20"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A20:F20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -823,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -847,18 +1121,18 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Yellow cells are for you to fill in. Everything else is provided.</t>
+          <t>🟡 Yellow cell = type something here.   🔵 Blue text = a given input.   Black text = a formula already provided.</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>Cash Flow ($)</t>
         </is>
@@ -936,19 +1210,55 @@
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Task: B13 = NPV(rate, years 1-3) plus the year-0 outlay added separately. B14 = IRR of all four cash flows (year 0 through year 3) in one range.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
+          <t>✏️  YOUR TASK</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="54" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>1. In B13, use NPV to discount the Year 1-3 cash flows (B7:B9) at the rate in B11, THEN add the Year 0 outlay (B6) separately — NPV() assumes its first value happens one period from now, not today.</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="n"/>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>2. In B14, use IRR on all four cash flows in one range: B6:B9 (Year 0 through Year 3, outlay included this time).</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>💡 If NPV &gt; 0, the project beats the discount rate. Compare IRR to the discount rate (8%) for the same read.</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="n"/>
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="14" t="n"/>
+      <c r="E19" s="14" t="n"/>
+      <c r="F19" s="15" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="7">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F17"/>
-    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -958,7 +1268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -982,7 +1292,7 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Yellow cells are for you to fill in. Everything else is provided.</t>
+          <t>🟡 Yellow cell = type something here.   🔵 Blue text = a given input.   Black text = a formula already provided.</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1329,12 @@
     </row>
     <row r="8"/>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>FCF</t>
         </is>
@@ -1072,33 +1382,54 @@
     <row r="15"/>
     <row r="16"/>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Try it yourself:</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>1. Goal Seek: Data &gt; What-If Analysis &gt; Goal Seek. Set B14 to 0 by changing B6 — what growth rate makes this project break even?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2. Data Table: list a range of WACC values down a column and growth rates across a row around B14, then Data &gt; What-If Analysis &gt; Data Table, using B7 as the row input cell and B6 as the column input cell.</t>
-        </is>
-      </c>
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>✏️  YOUR TASK</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>1. Goal Seek: Data tab &gt; What-If Analysis &gt; Goal Seek. Set cell B14 to value 0 by changing cell B6. This finds the growth rate at which the project exactly breaks even.</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="n"/>
+    </row>
+    <row r="19" ht="72" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>2. Data Table: pick a blank area, list a few WACC values down one column and a few growth rates across one row, with B14 in the top-left corner of that range. Select the whole range, then Data &gt; What-If Analysis &gt; Data Table — use B7 as the 'Row input cell' and B6 as the 'Column input cell'.</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>💡 This model (B5:B14) is already fully built with working formulas — there's nothing to fill in here, just run the two tools above on it.</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="n"/>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="14" t="n"/>
+      <c r="E20" s="14" t="n"/>
+      <c r="F20" s="15" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A20:F20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1127,22 +1458,22 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Module</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Cell</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>Correct formula</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Live check</t>
         </is>
@@ -1159,7 +1490,7 @@
           <t>B9 (Future value)</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
         <is>
           <t>ƒ =FV(B6,B7,0,-B5)</t>
         </is>
@@ -1180,7 +1511,7 @@
           <t>row 11 (Period 1, worked)</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>ƒ =-PMT($B$6/12,$B$7,$B$5) etc. — see the sheet</t>
         </is>
@@ -1201,7 +1532,7 @@
           <t>B13 (NPV)</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>ƒ =NPV(B11,B7:B9)+B6</t>
         </is>
@@ -1222,7 +1553,7 @@
           <t>B14 (IRR)</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>ƒ =IRR(B6:B9)</t>
         </is>
@@ -1233,7 +1564,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>Note: 'Live check' pulls today's value from your own sheet, so once you fill in the yellow cells correctly it will match what you typed. C4 has no single right answer — it's an exploration exercise.</t>
         </is>
